--- a/public/sample_uploads/capital_commitments.xlsx
+++ b/public/sample_uploads/capital_commitments.xlsx
@@ -470,12 +470,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Author:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Optional: only for a commitment that comes in through a feeder fund. Enter the feeder fund's name exactly as it is on CapHive; it must be a feeder fund of the fund in column A. Leave blank for a direct commitment. Omit this column entirely to leave the feeder fund of existing commitments unchanged on an Update Only import.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="38">
   <si>
     <t>Stakeholder *</t>
   </si>
@@ -586,6 +609,9 @@
   </si>
   <si>
     <t>Investor 6</t>
+  </si>
+  <si>
+    <t>Feeder Fund</t>
   </si>
 </sst>
 </file>
@@ -969,7 +995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.5625" style="1" customWidth="1"/>
@@ -991,10 +1017,11 @@
     <col min="17" max="17" width="5.1875" style="1" customWidth="1"/>
     <col min="18" max="18" width="10.8125" style="1" customWidth="1"/>
     <col min="19" max="19" width="8.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="1"/>
+    <col min="20" max="20" width="16.5" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1052,8 +1079,11 @@
       <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+      <c r="T1" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -1092,7 +1122,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1131,7 +1161,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -1170,7 +1200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -1209,7 +1239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -1248,7 +1278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -1287,7 +1317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1326,7 +1356,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
@@ -1365,28 +1395,28 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="M12" s="10"/>
     </row>
-    <row r="13" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="M13" s="10"/>
     </row>
-    <row r="14" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:19" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" ht="13.5" x14ac:dyDescent="0.35">
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="M16" s="10"/>
